--- a/questionnaire_templates/009_health_information_sharing_preferences_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/009_health_information_sharing_preferences_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,8 +658,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -687,12 +687,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'family_member',_'description':_'health_care_provider_or_family_member_',_'required':_true}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Family Member', 'description': 'Health care provider or family member ', 'required': True}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'authorized_representative',_'description':_'authorized_representative_(e.g._friend,_colleague,_legal_guardian)_',_'required':_false}</t>
+          <t>authorized_representative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Authorized Representative', 'description': 'Authorized representative (e.g. friend, colleague, legal guardian) ', 'required': False}</t>
+          <t>Authorized Representative</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'description':_'other_-_please_specify',_'required':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other', 'description': 'Other - please specify', 'required': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -738,12 +738,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'share_with_health_care_providers'}</t>
+          <t>share_with_health_care_providers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Share with health care providers'}</t>
+          <t>Share with health care providers</t>
         </is>
       </c>
     </row>
@@ -755,12 +755,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'share_with_insurance_companies'}</t>
+          <t>share_with_insurance_companies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Share with insurance companies'}</t>
+          <t>Share with insurance companies</t>
         </is>
       </c>
     </row>
@@ -772,12 +772,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'share_with_government_agencies'}</t>
+          <t>share_with_government_agencies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Share with government agencies'}</t>
+          <t>Share with government agencies</t>
         </is>
       </c>
     </row>
@@ -789,12 +789,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'share_with_research_institutions'}</t>
+          <t>share_with_research_institutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Share with research institutions'}</t>
+          <t>Share with research institutions</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'share_with_family_members'}</t>
+          <t>share_with_family_members</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Share with family members'}</t>
+          <t>Share with family members</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'share_with_friends_and_family'}</t>
+          <t>share_with_friends_and_family</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Share with friends and family'}</t>
+          <t>Share with friends and family</t>
         </is>
       </c>
     </row>
@@ -840,12 +840,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'share_with_other'}</t>
+          <t>share_with_other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'Share with other'}</t>
+          <t>Share with other</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'do_not_share'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'Do not share'}</t>
+          <t>Do not share</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'treatment_and_care'}</t>
+          <t>treatment_and_care</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Treatment and Care'}</t>
+          <t>Treatment and Care</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'research_and_study'}</t>
+          <t>research_and_study</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Research and Study'}</t>
+          <t>Research and Study</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'billing_and_insurance'}</t>
+          <t>billing_and_insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Billing and Insurance'}</t>
+          <t>Billing and Insurance</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'government_and_administrative'}</t>
+          <t>government_and_administrative</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Government and Administrative'}</t>
+          <t>Government and Administrative</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'do_not_share'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Do not share'}</t>
+          <t>Do not share</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'time-sensitive_data'}</t>
+          <t>time-sensitive_data</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Time-sensitive data'}</t>
+          <t>Time-sensitive data</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'sensitive_data'}</t>
+          <t>sensitive_data</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Sensitive data'}</t>
+          <t>Sensitive data</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'location_data'}</t>
+          <t>location_data</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Location data'}</t>
+          <t>Location data</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'do_not_share'}</t>
+          <t>do_not_share</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Do not share'}</t>
+          <t>Do not share</t>
         </is>
       </c>
     </row>
